--- a/docs/resources/Dictionary_testNetwork.xlsx
+++ b/docs/resources/Dictionary_testNetwork.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brend\Molgenis\repos\molgenis-emx2\docs\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E0291D-0A1C-401F-8DE7-2A64BE49F1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95820430-58B7-4ED1-A67E-4D51CFE99771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="11985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Datasets" sheetId="6" r:id="rId1"/>
+    <sheet name="Tables" sheetId="6" r:id="rId1"/>
     <sheet name="Variables" sheetId="9" r:id="rId2"/>
     <sheet name="Variable values" sheetId="14" r:id="rId3"/>
   </sheets>
@@ -36,9 +36,6 @@
     <t>name</t>
   </si>
   <si>
-    <t>dataset type</t>
-  </si>
-  <si>
     <t>unit of observation</t>
   </si>
   <si>
@@ -66,9 +63,6 @@
     <t>ontology term URI</t>
   </si>
   <si>
-    <t>dataset</t>
-  </si>
-  <si>
     <t>format</t>
   </si>
   <si>
@@ -111,9 +105,6 @@
     <t>useExternalDefinition.resource</t>
   </si>
   <si>
-    <t>useExternalDefinition.dataset</t>
-  </si>
-  <si>
     <t>useExternalDefinition.name</t>
   </si>
   <si>
@@ -952,6 +943,15 @@
   </si>
   <si>
     <t>variable</t>
+  </si>
+  <si>
+    <t>table type</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>useExternalDefinition.table</t>
   </si>
 </sst>
 </file>
@@ -1324,21 +1324,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.9296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.06640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1349,42 +1349,42 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
       </c>
       <c r="G1" t="s">
         <v>1</v>
       </c>
       <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
+      <c r="G2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1395,34 +1395,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:S87"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.9296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="216.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="73.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="216.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.06640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="24.1328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.109375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.1328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>308</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
@@ -1434,75 +1434,75 @@
         <v>1</v>
       </c>
       <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>17</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>18</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" t="s">
         <v>19</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>309</v>
+      </c>
+      <c r="R1" t="s">
+        <v>27</v>
+      </c>
+      <c r="S1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" t="s">
+        <v>298</v>
+      </c>
+      <c r="H2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
         <v>299</v>
-      </c>
-      <c r="F2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" t="s">
-        <v>301</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" t="s">
-        <v>302</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -1511,33 +1511,33 @@
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -1546,2011 +1546,2011 @@
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
         <v>32</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D5" t="s">
         <v>33</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E5" t="s">
         <v>34</v>
       </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>35</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>36</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E6" t="s">
         <v>37</v>
       </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
         <v>38</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>39</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>40</v>
       </c>
-      <c r="F6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
         <v>41</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>42</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" t="s">
         <v>43</v>
       </c>
-      <c r="F7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D9" t="s">
         <v>44</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" t="s">
         <v>45</v>
       </c>
-      <c r="E8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D10" t="s">
         <v>46</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
         <v>47</v>
       </c>
-      <c r="E9" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="D11" t="s">
         <v>48</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E11" t="s">
         <v>49</v>
       </c>
-      <c r="E10" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
         <v>50</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>51</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
         <v>52</v>
       </c>
-      <c r="F11" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="F12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
         <v>53</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D13" t="s">
         <v>54</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
         <v>55</v>
       </c>
-      <c r="F12" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="F13" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
         <v>56</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D14" t="s">
         <v>57</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>58</v>
       </c>
-      <c r="F13" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="F14" t="s">
         <v>59</v>
       </c>
-      <c r="D14" t="s">
+      <c r="H14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
         <v>60</v>
       </c>
-      <c r="E14" t="s">
+      <c r="D15" t="s">
         <v>61</v>
       </c>
-      <c r="F14" t="s">
+      <c r="E15" t="s">
         <v>62</v>
       </c>
-      <c r="H14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="F15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
         <v>63</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D16" t="s">
         <v>64</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E16" t="s">
         <v>65</v>
       </c>
-      <c r="F15" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="F16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
         <v>66</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D17" t="s">
         <v>67</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E17" t="s">
         <v>68</v>
       </c>
-      <c r="F16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="F17" t="s">
         <v>69</v>
       </c>
-      <c r="D17" t="s">
+      <c r="G17" t="s">
         <v>70</v>
       </c>
-      <c r="E17" t="s">
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
         <v>71</v>
       </c>
-      <c r="F17" t="s">
+      <c r="D18" t="s">
         <v>72</v>
       </c>
-      <c r="G17" t="s">
+      <c r="E18" t="s">
         <v>73</v>
       </c>
-      <c r="H17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="F18" t="s">
+        <v>31</v>
+      </c>
+      <c r="H18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
         <v>74</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D19" t="s">
         <v>75</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E19" t="s">
         <v>76</v>
       </c>
-      <c r="F18" t="s">
-        <v>34</v>
-      </c>
-      <c r="H18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="F19" t="s">
+        <v>31</v>
+      </c>
+      <c r="H19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
         <v>77</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D20" t="s">
         <v>78</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E20" t="s">
         <v>79</v>
       </c>
-      <c r="F19" t="s">
-        <v>34</v>
-      </c>
-      <c r="H19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="F20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" t="s">
         <v>80</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D21" t="s">
         <v>81</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E21" t="s">
         <v>82</v>
       </c>
-      <c r="F20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="F21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
         <v>83</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D22" t="s">
         <v>84</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E22" t="s">
         <v>85</v>
       </c>
-      <c r="F21" t="s">
-        <v>34</v>
-      </c>
-      <c r="H21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="F22" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" t="s">
         <v>86</v>
       </c>
-      <c r="D22" t="s">
+      <c r="H22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
         <v>87</v>
       </c>
-      <c r="E22" t="s">
+      <c r="D23" t="s">
         <v>88</v>
       </c>
-      <c r="F22" t="s">
-        <v>72</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="E23" t="s">
         <v>89</v>
       </c>
-      <c r="H22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="F23" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
         <v>90</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D24" t="s">
         <v>91</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E24" t="s">
         <v>92</v>
       </c>
-      <c r="F23" t="s">
-        <v>34</v>
-      </c>
-      <c r="H23" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="F24" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
         <v>93</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>94</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E25" t="s">
         <v>95</v>
       </c>
-      <c r="F24" t="s">
-        <v>72</v>
-      </c>
-      <c r="G24" t="s">
-        <v>89</v>
-      </c>
-      <c r="H24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="F25" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" t="s">
         <v>96</v>
       </c>
-      <c r="D25" t="s">
+      <c r="H25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
         <v>97</v>
       </c>
-      <c r="E25" t="s">
+      <c r="D26" t="s">
         <v>98</v>
       </c>
-      <c r="F25" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="E26" t="s">
         <v>99</v>
       </c>
-      <c r="H25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="F26" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" t="s">
+        <v>96</v>
+      </c>
+      <c r="H26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
         <v>100</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>101</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E27" t="s">
         <v>102</v>
       </c>
-      <c r="F26" t="s">
-        <v>72</v>
-      </c>
-      <c r="G26" t="s">
-        <v>99</v>
-      </c>
-      <c r="H26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="F27" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
         <v>103</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>104</v>
       </c>
-      <c r="E27" t="s">
+      <c r="E28" t="s">
         <v>105</v>
       </c>
-      <c r="F27" t="s">
-        <v>72</v>
-      </c>
-      <c r="G27" t="s">
-        <v>99</v>
-      </c>
-      <c r="H27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="F28" t="s">
+        <v>69</v>
+      </c>
+      <c r="G28" t="s">
+        <v>86</v>
+      </c>
+      <c r="H28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
         <v>106</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>107</v>
       </c>
-      <c r="E28" t="s">
+      <c r="E29" t="s">
         <v>108</v>
       </c>
-      <c r="F28" t="s">
-        <v>72</v>
-      </c>
-      <c r="G28" t="s">
-        <v>89</v>
-      </c>
-      <c r="H28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="F29" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" t="s">
         <v>109</v>
       </c>
-      <c r="D29" t="s">
+      <c r="H29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
         <v>110</v>
       </c>
-      <c r="E29" t="s">
+      <c r="D30" t="s">
         <v>111</v>
       </c>
-      <c r="F29" t="s">
-        <v>72</v>
-      </c>
-      <c r="G29" t="s">
+      <c r="E30" t="s">
         <v>112</v>
       </c>
-      <c r="H29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B30" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="F30" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" t="s">
+        <v>109</v>
+      </c>
+      <c r="H30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
         <v>113</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>114</v>
       </c>
-      <c r="E30" t="s">
+      <c r="E31" t="s">
         <v>115</v>
       </c>
-      <c r="F30" t="s">
-        <v>72</v>
-      </c>
-      <c r="G30" t="s">
-        <v>112</v>
-      </c>
-      <c r="H30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="F31" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" t="s">
+        <v>109</v>
+      </c>
+      <c r="H31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" t="s">
         <v>116</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D32" t="s">
         <v>117</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E32" t="s">
         <v>118</v>
       </c>
-      <c r="F31" t="s">
-        <v>72</v>
-      </c>
-      <c r="G31" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="F32" t="s">
+        <v>69</v>
+      </c>
+      <c r="G32" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" t="s">
         <v>119</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>120</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E33" t="s">
         <v>121</v>
       </c>
-      <c r="F32" t="s">
-        <v>72</v>
-      </c>
-      <c r="G32" t="s">
-        <v>112</v>
-      </c>
-      <c r="H32" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="F33" t="s">
+        <v>69</v>
+      </c>
+      <c r="G33" t="s">
         <v>122</v>
       </c>
-      <c r="D33" t="s">
+      <c r="H33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
         <v>123</v>
       </c>
-      <c r="E33" t="s">
+      <c r="D34" t="s">
         <v>124</v>
       </c>
-      <c r="F33" t="s">
-        <v>72</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="E34" t="s">
         <v>125</v>
       </c>
-      <c r="H33" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" t="s">
-        <v>24</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="F34" t="s">
+        <v>69</v>
+      </c>
+      <c r="G34" t="s">
         <v>126</v>
       </c>
-      <c r="D34" t="s">
+      <c r="H34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" t="s">
         <v>127</v>
       </c>
-      <c r="E34" t="s">
+      <c r="D35" t="s">
         <v>128</v>
       </c>
-      <c r="F34" t="s">
-        <v>72</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="E35" t="s">
         <v>129</v>
       </c>
-      <c r="H34" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" t="s">
-        <v>24</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="F35" t="s">
+        <v>69</v>
+      </c>
+      <c r="G35" t="s">
         <v>130</v>
       </c>
-      <c r="D35" t="s">
+      <c r="H35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" t="s">
         <v>131</v>
       </c>
-      <c r="E35" t="s">
+      <c r="D36" t="s">
         <v>132</v>
       </c>
-      <c r="F35" t="s">
-        <v>72</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="E36" t="s">
         <v>133</v>
       </c>
-      <c r="H35" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>23</v>
-      </c>
-      <c r="B36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="F36" t="s">
+        <v>69</v>
+      </c>
+      <c r="G36" t="s">
         <v>134</v>
       </c>
-      <c r="D36" t="s">
+      <c r="H36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" t="s">
         <v>135</v>
       </c>
-      <c r="E36" t="s">
+      <c r="D37" t="s">
+        <v>303</v>
+      </c>
+      <c r="E37" t="s">
         <v>136</v>
       </c>
-      <c r="F36" t="s">
-        <v>72</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="F37" t="s">
+        <v>69</v>
+      </c>
+      <c r="G37" t="s">
+        <v>130</v>
+      </c>
+      <c r="H37" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
         <v>137</v>
       </c>
-      <c r="H36" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>23</v>
-      </c>
-      <c r="B37" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="D38" t="s">
         <v>138</v>
       </c>
-      <c r="D37" t="s">
-        <v>306</v>
-      </c>
-      <c r="E37" t="s">
+      <c r="E38" t="s">
         <v>139</v>
       </c>
-      <c r="F37" t="s">
-        <v>72</v>
-      </c>
-      <c r="G37" t="s">
-        <v>133</v>
-      </c>
-      <c r="H37" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>23</v>
-      </c>
-      <c r="B38" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="F38" t="s">
+        <v>69</v>
+      </c>
+      <c r="G38" t="s">
+        <v>134</v>
+      </c>
+      <c r="H38" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" t="s">
+        <v>22</v>
+      </c>
+      <c r="C39" t="s">
         <v>140</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D39" t="s">
         <v>141</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E39" t="s">
         <v>142</v>
       </c>
-      <c r="F38" t="s">
-        <v>72</v>
-      </c>
-      <c r="G38" t="s">
-        <v>137</v>
-      </c>
-      <c r="H38" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>23</v>
-      </c>
-      <c r="B39" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="F39" t="s">
+        <v>69</v>
+      </c>
+      <c r="G39" t="s">
+        <v>70</v>
+      </c>
+      <c r="H39" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" t="s">
         <v>143</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D40" t="s">
         <v>144</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E40" t="s">
         <v>145</v>
       </c>
-      <c r="F39" t="s">
-        <v>72</v>
-      </c>
-      <c r="G39" t="s">
-        <v>73</v>
-      </c>
-      <c r="H39" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>23</v>
-      </c>
-      <c r="B40" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="F40" t="s">
+        <v>69</v>
+      </c>
+      <c r="G40" t="s">
+        <v>70</v>
+      </c>
+      <c r="H40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" t="s">
         <v>146</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
         <v>147</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E41" t="s">
         <v>148</v>
       </c>
-      <c r="F40" t="s">
-        <v>72</v>
-      </c>
-      <c r="G40" t="s">
-        <v>73</v>
-      </c>
-      <c r="H40" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>23</v>
-      </c>
-      <c r="B41" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="F41" t="s">
+        <v>69</v>
+      </c>
+      <c r="G41" t="s">
+        <v>70</v>
+      </c>
+      <c r="H41" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
         <v>149</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>150</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E42" t="s">
         <v>151</v>
       </c>
-      <c r="F41" t="s">
-        <v>72</v>
-      </c>
-      <c r="G41" t="s">
-        <v>73</v>
-      </c>
-      <c r="H41" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>23</v>
-      </c>
-      <c r="B42" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="F42" t="s">
+        <v>31</v>
+      </c>
+      <c r="H42" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" t="s">
         <v>152</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D43" t="s">
         <v>153</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E43" t="s">
         <v>154</v>
       </c>
-      <c r="F42" t="s">
-        <v>34</v>
-      </c>
-      <c r="H42" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>23</v>
-      </c>
-      <c r="B43" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="F43" t="s">
+        <v>31</v>
+      </c>
+      <c r="H43" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" t="s">
         <v>155</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D44" t="s">
         <v>156</v>
       </c>
-      <c r="E43" t="s">
+      <c r="E44" t="s">
         <v>157</v>
       </c>
-      <c r="F43" t="s">
-        <v>34</v>
-      </c>
-      <c r="H43" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>23</v>
-      </c>
-      <c r="B44" t="s">
-        <v>24</v>
-      </c>
-      <c r="C44" t="s">
+      <c r="F44" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>21</v>
+      </c>
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" t="s">
         <v>158</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D45" t="s">
         <v>159</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E45" t="s">
         <v>160</v>
       </c>
-      <c r="F44" t="s">
-        <v>34</v>
-      </c>
-      <c r="H44" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>23</v>
-      </c>
-      <c r="B45" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" t="s">
+      <c r="F45" t="s">
+        <v>31</v>
+      </c>
+      <c r="H45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>21</v>
+      </c>
+      <c r="B46" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" t="s">
         <v>161</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D46" t="s">
         <v>162</v>
       </c>
-      <c r="E45" t="s">
+      <c r="E46" t="s">
         <v>163</v>
       </c>
-      <c r="F45" t="s">
-        <v>34</v>
-      </c>
-      <c r="H45" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>23</v>
-      </c>
-      <c r="B46" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="F46" t="s">
+        <v>31</v>
+      </c>
+      <c r="H46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>21</v>
+      </c>
+      <c r="B47" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" t="s">
         <v>164</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>165</v>
       </c>
-      <c r="E46" t="s">
+      <c r="E47" t="s">
         <v>166</v>
       </c>
-      <c r="F46" t="s">
-        <v>34</v>
-      </c>
-      <c r="H46" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>23</v>
-      </c>
-      <c r="B47" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="F47" t="s">
+        <v>69</v>
+      </c>
+      <c r="G47" t="s">
+        <v>70</v>
+      </c>
+      <c r="H47" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" t="s">
         <v>167</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D48" t="s">
         <v>168</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E48" t="s">
         <v>169</v>
       </c>
-      <c r="F47" t="s">
-        <v>72</v>
-      </c>
-      <c r="G47" t="s">
-        <v>73</v>
-      </c>
-      <c r="H47" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>23</v>
-      </c>
-      <c r="B48" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="F48" t="s">
+        <v>31</v>
+      </c>
+      <c r="H48" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" t="s">
         <v>170</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>171</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E49" t="s">
         <v>172</v>
       </c>
-      <c r="F48" t="s">
-        <v>34</v>
-      </c>
-      <c r="H48" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>23</v>
-      </c>
-      <c r="B49" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" t="s">
+      <c r="F49" t="s">
+        <v>31</v>
+      </c>
+      <c r="H49" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>21</v>
+      </c>
+      <c r="B50" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" t="s">
         <v>173</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D50" t="s">
         <v>174</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E50" t="s">
         <v>175</v>
       </c>
-      <c r="F49" t="s">
-        <v>34</v>
-      </c>
-      <c r="H49" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="F50" t="s">
+        <v>31</v>
+      </c>
+      <c r="H50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>21</v>
+      </c>
+      <c r="B51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" t="s">
         <v>176</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D51" t="s">
         <v>177</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E51" t="s">
         <v>178</v>
       </c>
-      <c r="F50" t="s">
-        <v>34</v>
-      </c>
-      <c r="H50" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>23</v>
-      </c>
-      <c r="B51" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="F51" t="s">
+        <v>31</v>
+      </c>
+      <c r="H51" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>21</v>
+      </c>
+      <c r="B52" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" t="s">
         <v>179</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D52" t="s">
         <v>180</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E52" t="s">
         <v>181</v>
       </c>
-      <c r="F51" t="s">
-        <v>34</v>
-      </c>
-      <c r="H51" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>23</v>
-      </c>
-      <c r="B52" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="F52" t="s">
+        <v>31</v>
+      </c>
+      <c r="H52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" t="s">
         <v>182</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D53" t="s">
         <v>183</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E53" t="s">
         <v>184</v>
       </c>
-      <c r="F52" t="s">
-        <v>34</v>
-      </c>
-      <c r="H52" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>23</v>
-      </c>
-      <c r="B53" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" t="s">
+      <c r="F53" t="s">
+        <v>31</v>
+      </c>
+      <c r="H53" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>21</v>
+      </c>
+      <c r="B54" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" t="s">
         <v>185</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D54" t="s">
         <v>186</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E54" t="s">
         <v>187</v>
       </c>
-      <c r="F53" t="s">
-        <v>34</v>
-      </c>
-      <c r="H53" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>23</v>
-      </c>
-      <c r="B54" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" t="s">
+      <c r="F54" t="s">
+        <v>31</v>
+      </c>
+      <c r="H54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>21</v>
+      </c>
+      <c r="B55" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" t="s">
         <v>188</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D55" t="s">
         <v>189</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E55" t="s">
         <v>190</v>
       </c>
-      <c r="F54" t="s">
-        <v>34</v>
-      </c>
-      <c r="H54" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A55" t="s">
-        <v>23</v>
-      </c>
-      <c r="B55" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" t="s">
+      <c r="F55" t="s">
+        <v>69</v>
+      </c>
+      <c r="G55" t="s">
         <v>191</v>
       </c>
-      <c r="D55" t="s">
+      <c r="H55" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>21</v>
+      </c>
+      <c r="B56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" t="s">
         <v>192</v>
       </c>
-      <c r="E55" t="s">
+      <c r="D56" t="s">
         <v>193</v>
       </c>
-      <c r="F55" t="s">
-        <v>72</v>
-      </c>
-      <c r="G55" t="s">
+      <c r="E56" t="s">
         <v>194</v>
       </c>
-      <c r="H55" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B56" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="F56" t="s">
+        <v>31</v>
+      </c>
+      <c r="H56" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>21</v>
+      </c>
+      <c r="B57" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" t="s">
         <v>195</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D57" t="s">
         <v>196</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E57" t="s">
         <v>197</v>
       </c>
-      <c r="F56" t="s">
-        <v>34</v>
-      </c>
-      <c r="H56" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>23</v>
-      </c>
-      <c r="B57" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="F57" t="s">
+        <v>31</v>
+      </c>
+      <c r="H57" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>21</v>
+      </c>
+      <c r="B58" t="s">
+        <v>22</v>
+      </c>
+      <c r="C58" t="s">
         <v>198</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D58" t="s">
         <v>199</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E58" t="s">
         <v>200</v>
       </c>
-      <c r="F57" t="s">
-        <v>34</v>
-      </c>
-      <c r="H57" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A58" t="s">
-        <v>23</v>
-      </c>
-      <c r="B58" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" t="s">
+      <c r="F58" t="s">
+        <v>31</v>
+      </c>
+      <c r="H58" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>21</v>
+      </c>
+      <c r="B59" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" t="s">
         <v>201</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D59" t="s">
         <v>202</v>
       </c>
-      <c r="E58" t="s">
+      <c r="E59" t="s">
         <v>203</v>
       </c>
-      <c r="F58" t="s">
-        <v>34</v>
-      </c>
-      <c r="H58" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
-        <v>23</v>
-      </c>
-      <c r="B59" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" t="s">
+      <c r="F59" t="s">
+        <v>31</v>
+      </c>
+      <c r="H59" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>21</v>
+      </c>
+      <c r="B60" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" t="s">
         <v>204</v>
       </c>
-      <c r="D59" t="s">
+      <c r="D60" t="s">
         <v>205</v>
       </c>
-      <c r="E59" t="s">
+      <c r="E60" t="s">
         <v>206</v>
       </c>
-      <c r="F59" t="s">
-        <v>34</v>
-      </c>
-      <c r="H59" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A60" t="s">
-        <v>23</v>
-      </c>
-      <c r="B60" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" t="s">
+      <c r="F60" t="s">
+        <v>31</v>
+      </c>
+      <c r="H60" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>21</v>
+      </c>
+      <c r="B61" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" t="s">
         <v>207</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D61" t="s">
         <v>208</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E61" t="s">
         <v>209</v>
       </c>
-      <c r="F60" t="s">
-        <v>34</v>
-      </c>
-      <c r="H60" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A61" t="s">
-        <v>23</v>
-      </c>
-      <c r="B61" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" t="s">
+      <c r="F61" t="s">
+        <v>31</v>
+      </c>
+      <c r="H61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>21</v>
+      </c>
+      <c r="B62" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" t="s">
         <v>210</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D62" t="s">
         <v>211</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E62" t="s">
         <v>212</v>
       </c>
-      <c r="F61" t="s">
-        <v>34</v>
-      </c>
-      <c r="H61" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A62" t="s">
-        <v>23</v>
-      </c>
-      <c r="B62" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="F62" t="s">
+        <v>31</v>
+      </c>
+      <c r="H62" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>21</v>
+      </c>
+      <c r="B63" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" t="s">
         <v>213</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D63" t="s">
         <v>214</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E63" t="s">
         <v>215</v>
       </c>
-      <c r="F62" t="s">
-        <v>34</v>
-      </c>
-      <c r="H62" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A63" t="s">
-        <v>23</v>
-      </c>
-      <c r="B63" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="F63" t="s">
+        <v>31</v>
+      </c>
+      <c r="H63" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>21</v>
+      </c>
+      <c r="B64" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64" t="s">
         <v>216</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D64" t="s">
         <v>217</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E64" t="s">
         <v>218</v>
       </c>
-      <c r="F63" t="s">
-        <v>34</v>
-      </c>
-      <c r="H63" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A64" t="s">
-        <v>23</v>
-      </c>
-      <c r="B64" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="F64" t="s">
+        <v>69</v>
+      </c>
+      <c r="G64" t="s">
+        <v>191</v>
+      </c>
+      <c r="H64" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>21</v>
+      </c>
+      <c r="B65" t="s">
+        <v>22</v>
+      </c>
+      <c r="C65" t="s">
         <v>219</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D65" t="s">
         <v>220</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E65" t="s">
         <v>221</v>
       </c>
-      <c r="F64" t="s">
-        <v>72</v>
-      </c>
-      <c r="G64" t="s">
-        <v>194</v>
-      </c>
-      <c r="H64" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A65" t="s">
-        <v>23</v>
-      </c>
-      <c r="B65" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" t="s">
+      <c r="F65" t="s">
+        <v>59</v>
+      </c>
+      <c r="H65" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>21</v>
+      </c>
+      <c r="B66" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" t="s">
         <v>222</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D66" t="s">
         <v>223</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E66" t="s">
         <v>224</v>
       </c>
-      <c r="F65" t="s">
-        <v>62</v>
-      </c>
-      <c r="H65" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A66" t="s">
-        <v>23</v>
-      </c>
-      <c r="B66" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="F66" t="s">
+        <v>69</v>
+      </c>
+      <c r="G66" t="s">
+        <v>191</v>
+      </c>
+      <c r="H66" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>21</v>
+      </c>
+      <c r="B67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67" t="s">
         <v>225</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D67" t="s">
         <v>226</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E67" t="s">
         <v>227</v>
       </c>
-      <c r="F66" t="s">
-        <v>72</v>
-      </c>
-      <c r="G66" t="s">
-        <v>194</v>
-      </c>
-      <c r="H66" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A67" t="s">
-        <v>23</v>
-      </c>
-      <c r="B67" t="s">
-        <v>24</v>
-      </c>
-      <c r="C67" t="s">
+      <c r="F67" t="s">
+        <v>59</v>
+      </c>
+      <c r="H67" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>21</v>
+      </c>
+      <c r="B68" t="s">
+        <v>22</v>
+      </c>
+      <c r="C68" t="s">
         <v>228</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D68" t="s">
         <v>229</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E68" t="s">
         <v>230</v>
       </c>
-      <c r="F67" t="s">
-        <v>62</v>
-      </c>
-      <c r="H67" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A68" t="s">
-        <v>23</v>
-      </c>
-      <c r="B68" t="s">
-        <v>24</v>
-      </c>
-      <c r="C68" t="s">
+      <c r="F68" t="s">
+        <v>31</v>
+      </c>
+      <c r="H68" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>21</v>
+      </c>
+      <c r="B69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" t="s">
         <v>231</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D69" t="s">
         <v>232</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E69" t="s">
         <v>233</v>
       </c>
-      <c r="F68" t="s">
-        <v>34</v>
-      </c>
-      <c r="H68" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A69" t="s">
-        <v>23</v>
-      </c>
-      <c r="B69" t="s">
-        <v>24</v>
-      </c>
-      <c r="C69" t="s">
+      <c r="F69" t="s">
+        <v>59</v>
+      </c>
+      <c r="H69" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>21</v>
+      </c>
+      <c r="B70" t="s">
+        <v>22</v>
+      </c>
+      <c r="C70" t="s">
         <v>234</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D70" t="s">
         <v>235</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E70" t="s">
         <v>236</v>
       </c>
-      <c r="F69" t="s">
-        <v>62</v>
-      </c>
-      <c r="H69" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A70" t="s">
-        <v>23</v>
-      </c>
-      <c r="B70" t="s">
-        <v>24</v>
-      </c>
-      <c r="C70" t="s">
+      <c r="F70" t="s">
+        <v>59</v>
+      </c>
+      <c r="H70" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>21</v>
+      </c>
+      <c r="B71" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" t="s">
         <v>237</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D71" t="s">
         <v>238</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E71" t="s">
         <v>239</v>
       </c>
-      <c r="F70" t="s">
-        <v>62</v>
-      </c>
-      <c r="H70" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A71" t="s">
-        <v>23</v>
-      </c>
-      <c r="B71" t="s">
-        <v>24</v>
-      </c>
-      <c r="C71" t="s">
+      <c r="F71" t="s">
+        <v>59</v>
+      </c>
+      <c r="H71" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>21</v>
+      </c>
+      <c r="B72" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" t="s">
         <v>240</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D72" t="s">
         <v>241</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E72" t="s">
         <v>242</v>
       </c>
-      <c r="F71" t="s">
-        <v>62</v>
-      </c>
-      <c r="H71" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A72" t="s">
-        <v>23</v>
-      </c>
-      <c r="B72" t="s">
-        <v>24</v>
-      </c>
-      <c r="C72" t="s">
+      <c r="F72" t="s">
+        <v>59</v>
+      </c>
+      <c r="H72" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>21</v>
+      </c>
+      <c r="B73" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" t="s">
         <v>243</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D73" t="s">
         <v>244</v>
       </c>
-      <c r="E72" t="s">
+      <c r="E73" t="s">
         <v>245</v>
       </c>
-      <c r="F72" t="s">
-        <v>62</v>
-      </c>
-      <c r="H72" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A73" t="s">
-        <v>23</v>
-      </c>
-      <c r="B73" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" t="s">
+      <c r="F73" t="s">
+        <v>59</v>
+      </c>
+      <c r="H73" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>21</v>
+      </c>
+      <c r="B74" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" t="s">
         <v>246</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D74" t="s">
         <v>247</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E74" t="s">
         <v>248</v>
       </c>
-      <c r="F73" t="s">
-        <v>62</v>
-      </c>
-      <c r="H73" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A74" t="s">
-        <v>23</v>
-      </c>
-      <c r="B74" t="s">
-        <v>24</v>
-      </c>
-      <c r="C74" t="s">
+      <c r="F74" t="s">
+        <v>69</v>
+      </c>
+      <c r="G74" t="s">
+        <v>191</v>
+      </c>
+      <c r="H74" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>21</v>
+      </c>
+      <c r="B75" t="s">
+        <v>22</v>
+      </c>
+      <c r="C75" t="s">
         <v>249</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D75" t="s">
         <v>250</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E75" t="s">
         <v>251</v>
       </c>
-      <c r="F74" t="s">
-        <v>72</v>
-      </c>
-      <c r="G74" t="s">
-        <v>194</v>
-      </c>
-      <c r="H74" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A75" t="s">
-        <v>23</v>
-      </c>
-      <c r="B75" t="s">
-        <v>24</v>
-      </c>
-      <c r="C75" t="s">
+      <c r="F75" t="s">
+        <v>31</v>
+      </c>
+      <c r="H75" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>21</v>
+      </c>
+      <c r="B76" t="s">
+        <v>22</v>
+      </c>
+      <c r="C76" t="s">
         <v>252</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D76" t="s">
         <v>253</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E76" t="s">
         <v>254</v>
       </c>
-      <c r="F75" t="s">
-        <v>34</v>
-      </c>
-      <c r="H75" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A76" t="s">
-        <v>23</v>
-      </c>
-      <c r="B76" t="s">
-        <v>24</v>
-      </c>
-      <c r="C76" t="s">
+      <c r="F76" t="s">
+        <v>31</v>
+      </c>
+      <c r="H76" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>21</v>
+      </c>
+      <c r="B77" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" t="s">
         <v>255</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D77" t="s">
         <v>256</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E77" t="s">
         <v>257</v>
       </c>
-      <c r="F76" t="s">
-        <v>34</v>
-      </c>
-      <c r="H76" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A77" t="s">
-        <v>23</v>
-      </c>
-      <c r="B77" t="s">
-        <v>24</v>
-      </c>
-      <c r="C77" t="s">
+      <c r="F77" t="s">
+        <v>31</v>
+      </c>
+      <c r="H77" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>21</v>
+      </c>
+      <c r="B78" t="s">
+        <v>22</v>
+      </c>
+      <c r="C78" t="s">
         <v>258</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D78" t="s">
         <v>259</v>
       </c>
-      <c r="E77" t="s">
+      <c r="E78" t="s">
         <v>260</v>
       </c>
-      <c r="F77" t="s">
-        <v>34</v>
-      </c>
-      <c r="H77" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A78" t="s">
-        <v>23</v>
-      </c>
-      <c r="B78" t="s">
-        <v>24</v>
-      </c>
-      <c r="C78" t="s">
+      <c r="F78" t="s">
+        <v>31</v>
+      </c>
+      <c r="H78" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>21</v>
+      </c>
+      <c r="B79" t="s">
+        <v>22</v>
+      </c>
+      <c r="C79" t="s">
         <v>261</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D79" t="s">
         <v>262</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E79" t="s">
         <v>263</v>
       </c>
-      <c r="F78" t="s">
-        <v>34</v>
-      </c>
-      <c r="H78" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A79" t="s">
-        <v>23</v>
-      </c>
-      <c r="B79" t="s">
-        <v>24</v>
-      </c>
-      <c r="C79" t="s">
+      <c r="F79" t="s">
+        <v>31</v>
+      </c>
+      <c r="H79" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>21</v>
+      </c>
+      <c r="B80" t="s">
+        <v>22</v>
+      </c>
+      <c r="C80" t="s">
         <v>264</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D80" t="s">
         <v>265</v>
       </c>
-      <c r="E79" t="s">
+      <c r="E80" t="s">
         <v>266</v>
       </c>
-      <c r="F79" t="s">
-        <v>34</v>
-      </c>
-      <c r="H79" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A80" t="s">
-        <v>23</v>
-      </c>
-      <c r="B80" t="s">
-        <v>24</v>
-      </c>
-      <c r="C80" t="s">
+      <c r="F80" t="s">
+        <v>31</v>
+      </c>
+      <c r="H80" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>21</v>
+      </c>
+      <c r="B81" t="s">
+        <v>22</v>
+      </c>
+      <c r="C81" t="s">
         <v>267</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D81" t="s">
         <v>268</v>
       </c>
-      <c r="E80" t="s">
+      <c r="E81" t="s">
         <v>269</v>
       </c>
-      <c r="F80" t="s">
-        <v>34</v>
-      </c>
-      <c r="H80" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A81" t="s">
-        <v>23</v>
-      </c>
-      <c r="B81" t="s">
-        <v>24</v>
-      </c>
-      <c r="C81" t="s">
+      <c r="F81" t="s">
+        <v>31</v>
+      </c>
+      <c r="H81" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>21</v>
+      </c>
+      <c r="B82" t="s">
+        <v>22</v>
+      </c>
+      <c r="C82" t="s">
         <v>270</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D82" t="s">
         <v>271</v>
       </c>
-      <c r="E81" t="s">
+      <c r="E82" t="s">
         <v>272</v>
       </c>
-      <c r="F81" t="s">
-        <v>34</v>
-      </c>
-      <c r="H81" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A82" t="s">
-        <v>23</v>
-      </c>
-      <c r="B82" t="s">
-        <v>24</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="F82" t="s">
+        <v>31</v>
+      </c>
+      <c r="H82" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>21</v>
+      </c>
+      <c r="B83" t="s">
+        <v>22</v>
+      </c>
+      <c r="C83" t="s">
         <v>273</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D83" t="s">
         <v>274</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E83" t="s">
         <v>275</v>
       </c>
-      <c r="F82" t="s">
-        <v>34</v>
-      </c>
-      <c r="H82" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A83" t="s">
-        <v>23</v>
-      </c>
-      <c r="B83" t="s">
-        <v>24</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="F83" t="s">
+        <v>31</v>
+      </c>
+      <c r="H83" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>21</v>
+      </c>
+      <c r="B84" t="s">
+        <v>22</v>
+      </c>
+      <c r="C84" t="s">
         <v>276</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D84" t="s">
         <v>277</v>
       </c>
-      <c r="E83" t="s">
+      <c r="E84" t="s">
         <v>278</v>
       </c>
-      <c r="F83" t="s">
-        <v>34</v>
-      </c>
-      <c r="H83" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A84" t="s">
-        <v>23</v>
-      </c>
-      <c r="B84" t="s">
-        <v>24</v>
-      </c>
-      <c r="C84" t="s">
+      <c r="F84" t="s">
+        <v>31</v>
+      </c>
+      <c r="H84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>21</v>
+      </c>
+      <c r="B85" t="s">
+        <v>22</v>
+      </c>
+      <c r="C85" t="s">
         <v>279</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D85" t="s">
         <v>280</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E85" t="s">
         <v>281</v>
       </c>
-      <c r="F84" t="s">
-        <v>34</v>
-      </c>
-      <c r="H84" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A85" t="s">
-        <v>23</v>
-      </c>
-      <c r="B85" t="s">
-        <v>24</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="F85" t="s">
+        <v>31</v>
+      </c>
+      <c r="H85" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>21</v>
+      </c>
+      <c r="B86" t="s">
+        <v>22</v>
+      </c>
+      <c r="C86" t="s">
         <v>282</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D86" t="s">
         <v>283</v>
       </c>
-      <c r="E85" t="s">
+      <c r="E86" t="s">
         <v>284</v>
       </c>
-      <c r="F85" t="s">
-        <v>34</v>
-      </c>
-      <c r="H85" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A86" t="s">
-        <v>23</v>
-      </c>
-      <c r="B86" t="s">
-        <v>24</v>
-      </c>
-      <c r="C86" t="s">
+      <c r="F86" t="s">
+        <v>31</v>
+      </c>
+      <c r="H86" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>21</v>
+      </c>
+      <c r="B87" t="s">
+        <v>22</v>
+      </c>
+      <c r="C87" t="s">
         <v>285</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D87" t="s">
         <v>286</v>
       </c>
-      <c r="E86" t="s">
+      <c r="E87" t="s">
         <v>287</v>
       </c>
-      <c r="F86" t="s">
-        <v>34</v>
-      </c>
-      <c r="H86" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A87" t="s">
-        <v>23</v>
-      </c>
-      <c r="B87" t="s">
-        <v>24</v>
-      </c>
-      <c r="C87" t="s">
-        <v>288</v>
-      </c>
-      <c r="D87" t="s">
-        <v>289</v>
-      </c>
-      <c r="E87" t="s">
-        <v>290</v>
-      </c>
       <c r="F87" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H87" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -3561,130 +3561,130 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>308</v>
       </c>
       <c r="C1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
       </c>
       <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
       <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E2" t="s">
+        <v>289</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E3" t="s">
         <v>291</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
         <v>292</v>
       </c>
-      <c r="I2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E4" t="s">
         <v>293</v>
       </c>
-      <c r="E3" t="s">
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
         <v>294</v>
       </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E5" t="s">
         <v>295</v>
       </c>
-      <c r="E4" t="s">
-        <v>296</v>
-      </c>
-      <c r="I4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" t="s">
-        <v>297</v>
-      </c>
-      <c r="E5" t="s">
-        <v>298</v>
-      </c>
       <c r="I5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/docs/resources/Dictionary_testNetwork.xlsx
+++ b/docs/resources/Dictionary_testNetwork.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95820430-58B7-4ED1-A67E-4D51CFE99771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301311DE-E90B-4645-9FF2-BEA03B89E409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="311">
   <si>
     <t>label</t>
   </si>
@@ -952,6 +952,9 @@
   </si>
   <si>
     <t>useExternalDefinition.table</t>
+  </si>
+  <si>
+    <t>http://snomed.info/id/903121</t>
   </si>
 </sst>
 </file>
@@ -1394,30 +1397,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:S87"/>
+  <dimension ref="A1:T87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="216.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.5546875" customWidth="1"/>
+    <col min="5" max="5" width="60.21875" customWidth="1"/>
     <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="24.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1440,43 +1444,46 @@
         <v>14</v>
       </c>
       <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>15</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>16</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>17</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>18</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>5</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>19</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>309</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>27</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1499,19 +1506,22 @@
         <v>298</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" t="s">
+        <v>310</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
         <v>299</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1533,20 +1543,20 @@
       <c r="G3" t="s">
         <v>302</v>
       </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
         <v>299</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1565,11 +1575,11 @@
       <c r="F4" t="s">
         <v>31</v>
       </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1588,11 +1598,11 @@
       <c r="F5" t="s">
         <v>31</v>
       </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="I5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1611,11 +1621,11 @@
       <c r="F6" t="s">
         <v>31</v>
       </c>
-      <c r="H6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="I6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1634,11 +1644,11 @@
       <c r="F7" t="s">
         <v>31</v>
       </c>
-      <c r="H7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="I7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1657,11 +1667,11 @@
       <c r="F8" t="s">
         <v>31</v>
       </c>
-      <c r="H8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="I8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1680,11 +1690,11 @@
       <c r="F9" t="s">
         <v>31</v>
       </c>
-      <c r="H9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="I9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1703,11 +1713,11 @@
       <c r="F10" t="s">
         <v>31</v>
       </c>
-      <c r="H10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="I10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1726,11 +1736,11 @@
       <c r="F11" t="s">
         <v>31</v>
       </c>
-      <c r="H11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="I11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1749,11 +1759,11 @@
       <c r="F12" t="s">
         <v>31</v>
       </c>
-      <c r="H12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="I12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1772,11 +1782,11 @@
       <c r="F13" t="s">
         <v>31</v>
       </c>
-      <c r="H13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="I13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1795,11 +1805,11 @@
       <c r="F14" t="s">
         <v>59</v>
       </c>
-      <c r="H14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="I14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -1818,11 +1828,11 @@
       <c r="F15" t="s">
         <v>59</v>
       </c>
-      <c r="H15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="I15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1841,11 +1851,11 @@
       <c r="F16" t="s">
         <v>31</v>
       </c>
-      <c r="H16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1867,11 +1877,11 @@
       <c r="G17" t="s">
         <v>70</v>
       </c>
-      <c r="H17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1890,11 +1900,11 @@
       <c r="F18" t="s">
         <v>31</v>
       </c>
-      <c r="H18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1913,11 +1923,11 @@
       <c r="F19" t="s">
         <v>31</v>
       </c>
-      <c r="H19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1936,11 +1946,11 @@
       <c r="F20" t="s">
         <v>31</v>
       </c>
-      <c r="H20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1959,11 +1969,11 @@
       <c r="F21" t="s">
         <v>31</v>
       </c>
-      <c r="H21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1985,11 +1995,11 @@
       <c r="G22" t="s">
         <v>86</v>
       </c>
-      <c r="H22" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2008,11 +2018,11 @@
       <c r="F23" t="s">
         <v>31</v>
       </c>
-      <c r="H23" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -2034,11 +2044,11 @@
       <c r="G24" t="s">
         <v>86</v>
       </c>
-      <c r="H24" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -2060,11 +2070,11 @@
       <c r="G25" t="s">
         <v>96</v>
       </c>
-      <c r="H25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -2086,11 +2096,11 @@
       <c r="G26" t="s">
         <v>96</v>
       </c>
-      <c r="H26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -2112,11 +2122,11 @@
       <c r="G27" t="s">
         <v>96</v>
       </c>
-      <c r="H27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -2138,11 +2148,11 @@
       <c r="G28" t="s">
         <v>86</v>
       </c>
-      <c r="H28" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -2164,11 +2174,11 @@
       <c r="G29" t="s">
         <v>109</v>
       </c>
-      <c r="H29" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>21</v>
       </c>
@@ -2190,11 +2200,11 @@
       <c r="G30" t="s">
         <v>109</v>
       </c>
-      <c r="H30" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>21</v>
       </c>
@@ -2216,11 +2226,11 @@
       <c r="G31" t="s">
         <v>109</v>
       </c>
-      <c r="H31" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>21</v>
       </c>
@@ -2242,11 +2252,11 @@
       <c r="G32" t="s">
         <v>109</v>
       </c>
-      <c r="H32" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>21</v>
       </c>
@@ -2268,11 +2278,11 @@
       <c r="G33" t="s">
         <v>122</v>
       </c>
-      <c r="H33" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>21</v>
       </c>
@@ -2294,11 +2304,11 @@
       <c r="G34" t="s">
         <v>126</v>
       </c>
-      <c r="H34" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>21</v>
       </c>
@@ -2320,11 +2330,11 @@
       <c r="G35" t="s">
         <v>130</v>
       </c>
-      <c r="H35" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -2346,11 +2356,11 @@
       <c r="G36" t="s">
         <v>134</v>
       </c>
-      <c r="H36" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -2372,11 +2382,11 @@
       <c r="G37" t="s">
         <v>130</v>
       </c>
-      <c r="H37" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I37" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -2398,11 +2408,11 @@
       <c r="G38" t="s">
         <v>134</v>
       </c>
-      <c r="H38" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I38" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -2424,11 +2434,11 @@
       <c r="G39" t="s">
         <v>70</v>
       </c>
-      <c r="H39" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I39" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>21</v>
       </c>
@@ -2450,11 +2460,11 @@
       <c r="G40" t="s">
         <v>70</v>
       </c>
-      <c r="H40" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>21</v>
       </c>
@@ -2476,11 +2486,11 @@
       <c r="G41" t="s">
         <v>70</v>
       </c>
-      <c r="H41" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I41" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>21</v>
       </c>
@@ -2499,11 +2509,11 @@
       <c r="F42" t="s">
         <v>31</v>
       </c>
-      <c r="H42" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I42" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>21</v>
       </c>
@@ -2522,11 +2532,11 @@
       <c r="F43" t="s">
         <v>31</v>
       </c>
-      <c r="H43" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I43" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>21</v>
       </c>
@@ -2545,11 +2555,11 @@
       <c r="F44" t="s">
         <v>31</v>
       </c>
-      <c r="H44" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I44" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>21</v>
       </c>
@@ -2568,11 +2578,11 @@
       <c r="F45" t="s">
         <v>31</v>
       </c>
-      <c r="H45" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>21</v>
       </c>
@@ -2591,11 +2601,11 @@
       <c r="F46" t="s">
         <v>31</v>
       </c>
-      <c r="H46" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>21</v>
       </c>
@@ -2617,11 +2627,11 @@
       <c r="G47" t="s">
         <v>70</v>
       </c>
-      <c r="H47" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I47" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>21</v>
       </c>
@@ -2640,11 +2650,11 @@
       <c r="F48" t="s">
         <v>31</v>
       </c>
-      <c r="H48" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I48" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>21</v>
       </c>
@@ -2663,11 +2673,11 @@
       <c r="F49" t="s">
         <v>31</v>
       </c>
-      <c r="H49" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I49" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>21</v>
       </c>
@@ -2686,11 +2696,11 @@
       <c r="F50" t="s">
         <v>31</v>
       </c>
-      <c r="H50" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>21</v>
       </c>
@@ -2709,11 +2719,11 @@
       <c r="F51" t="s">
         <v>31</v>
       </c>
-      <c r="H51" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I51" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>21</v>
       </c>
@@ -2732,11 +2742,11 @@
       <c r="F52" t="s">
         <v>31</v>
       </c>
-      <c r="H52" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>21</v>
       </c>
@@ -2755,11 +2765,11 @@
       <c r="F53" t="s">
         <v>31</v>
       </c>
-      <c r="H53" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I53" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>21</v>
       </c>
@@ -2778,11 +2788,11 @@
       <c r="F54" t="s">
         <v>31</v>
       </c>
-      <c r="H54" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>21</v>
       </c>
@@ -2804,11 +2814,11 @@
       <c r="G55" t="s">
         <v>191</v>
       </c>
-      <c r="H55" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I55" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>21</v>
       </c>
@@ -2827,11 +2837,11 @@
       <c r="F56" t="s">
         <v>31</v>
       </c>
-      <c r="H56" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I56" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>21</v>
       </c>
@@ -2850,11 +2860,11 @@
       <c r="F57" t="s">
         <v>31</v>
       </c>
-      <c r="H57" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I57" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>21</v>
       </c>
@@ -2873,11 +2883,11 @@
       <c r="F58" t="s">
         <v>31</v>
       </c>
-      <c r="H58" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I58" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>21</v>
       </c>
@@ -2896,11 +2906,11 @@
       <c r="F59" t="s">
         <v>31</v>
       </c>
-      <c r="H59" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I59" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>21</v>
       </c>
@@ -2919,11 +2929,11 @@
       <c r="F60" t="s">
         <v>31</v>
       </c>
-      <c r="H60" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I60" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>21</v>
       </c>
@@ -2942,11 +2952,11 @@
       <c r="F61" t="s">
         <v>31</v>
       </c>
-      <c r="H61" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I61" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>21</v>
       </c>
@@ -2965,11 +2975,11 @@
       <c r="F62" t="s">
         <v>31</v>
       </c>
-      <c r="H62" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I62" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>21</v>
       </c>
@@ -2988,11 +2998,11 @@
       <c r="F63" t="s">
         <v>31</v>
       </c>
-      <c r="H63" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I63" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>21</v>
       </c>
@@ -3014,11 +3024,11 @@
       <c r="G64" t="s">
         <v>191</v>
       </c>
-      <c r="H64" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I64" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>21</v>
       </c>
@@ -3037,11 +3047,11 @@
       <c r="F65" t="s">
         <v>59</v>
       </c>
-      <c r="H65" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I65" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>21</v>
       </c>
@@ -3063,11 +3073,11 @@
       <c r="G66" t="s">
         <v>191</v>
       </c>
-      <c r="H66" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I66" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>21</v>
       </c>
@@ -3086,11 +3096,11 @@
       <c r="F67" t="s">
         <v>59</v>
       </c>
-      <c r="H67" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I67" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>21</v>
       </c>
@@ -3109,11 +3119,11 @@
       <c r="F68" t="s">
         <v>31</v>
       </c>
-      <c r="H68" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I68" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>21</v>
       </c>
@@ -3132,11 +3142,11 @@
       <c r="F69" t="s">
         <v>59</v>
       </c>
-      <c r="H69" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I69" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>21</v>
       </c>
@@ -3155,11 +3165,11 @@
       <c r="F70" t="s">
         <v>59</v>
       </c>
-      <c r="H70" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I70" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>21</v>
       </c>
@@ -3178,11 +3188,11 @@
       <c r="F71" t="s">
         <v>59</v>
       </c>
-      <c r="H71" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I71" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>21</v>
       </c>
@@ -3201,11 +3211,11 @@
       <c r="F72" t="s">
         <v>59</v>
       </c>
-      <c r="H72" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I72" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>21</v>
       </c>
@@ -3224,11 +3234,11 @@
       <c r="F73" t="s">
         <v>59</v>
       </c>
-      <c r="H73" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I73" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>21</v>
       </c>
@@ -3250,11 +3260,11 @@
       <c r="G74" t="s">
         <v>191</v>
       </c>
-      <c r="H74" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I74" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>21</v>
       </c>
@@ -3273,11 +3283,11 @@
       <c r="F75" t="s">
         <v>31</v>
       </c>
-      <c r="H75" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I75" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>21</v>
       </c>
@@ -3296,11 +3306,11 @@
       <c r="F76" t="s">
         <v>31</v>
       </c>
-      <c r="H76" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I76" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>21</v>
       </c>
@@ -3319,11 +3329,11 @@
       <c r="F77" t="s">
         <v>31</v>
       </c>
-      <c r="H77" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I77" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>21</v>
       </c>
@@ -3342,11 +3352,11 @@
       <c r="F78" t="s">
         <v>31</v>
       </c>
-      <c r="H78" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I78" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>21</v>
       </c>
@@ -3365,11 +3375,11 @@
       <c r="F79" t="s">
         <v>31</v>
       </c>
-      <c r="H79" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I79" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>21</v>
       </c>
@@ -3388,11 +3398,11 @@
       <c r="F80" t="s">
         <v>31</v>
       </c>
-      <c r="H80" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I80" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>21</v>
       </c>
@@ -3411,11 +3421,11 @@
       <c r="F81" t="s">
         <v>31</v>
       </c>
-      <c r="H81" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I81" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>21</v>
       </c>
@@ -3434,11 +3444,11 @@
       <c r="F82" t="s">
         <v>31</v>
       </c>
-      <c r="H82" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I82" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>21</v>
       </c>
@@ -3457,11 +3467,11 @@
       <c r="F83" t="s">
         <v>31</v>
       </c>
-      <c r="H83" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I83" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>21</v>
       </c>
@@ -3480,11 +3490,11 @@
       <c r="F84" t="s">
         <v>31</v>
       </c>
-      <c r="H84" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I84" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>21</v>
       </c>
@@ -3503,11 +3513,11 @@
       <c r="F85" t="s">
         <v>31</v>
       </c>
-      <c r="H85" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I85" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>21</v>
       </c>
@@ -3526,11 +3536,11 @@
       <c r="F86" t="s">
         <v>31</v>
       </c>
-      <c r="H86" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I86" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>21</v>
       </c>
@@ -3549,7 +3559,7 @@
       <c r="F87" t="s">
         <v>31</v>
       </c>
-      <c r="H87" t="s">
+      <c r="I87" t="s">
         <v>25</v>
       </c>
     </row>

--- a/docs/resources/Dictionary_testNetwork.xlsx
+++ b/docs/resources/Dictionary_testNetwork.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brend\Molgenis\repos\molgenis-emx2\docs\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E0291D-0A1C-401F-8DE7-2A64BE49F1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89ACE056-AAD2-4CAE-8285-59AB42B12C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="11985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datasets" sheetId="6" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="311">
   <si>
     <t>label</t>
   </si>
@@ -952,6 +952,9 @@
   </si>
   <si>
     <t>variable</t>
+  </si>
+  <si>
+    <t>http://snomed.info/id/903121</t>
   </si>
 </sst>
 </file>
@@ -1323,22 +1326,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.9296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.06640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1363,14 +1366,14 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1383,7 +1386,7 @@
       <c r="G2" t="s">
         <v>26</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1394,30 +1397,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:S87"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:T87"/>
+  <sheetFormatPr defaultColWidth="8.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.9296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="216.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.1328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.06640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="24.1328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5546875" customWidth="1"/>
+    <col min="5" max="5" width="39.21875" customWidth="1"/>
+    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1440,43 +1431,46 @@
         <v>16</v>
       </c>
       <c r="H1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>17</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>18</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>19</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>6</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>21</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>28</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>29</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>30</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1499,19 +1493,22 @@
         <v>301</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" t="s">
+        <v>310</v>
+      </c>
+      <c r="I2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
         <v>302</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1533,20 +1530,20 @@
       <c r="G3" t="s">
         <v>305</v>
       </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
         <v>302</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1565,11 +1562,11 @@
       <c r="F4" t="s">
         <v>34</v>
       </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1588,11 +1585,11 @@
       <c r="F5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1611,11 +1608,11 @@
       <c r="F6" t="s">
         <v>34</v>
       </c>
-      <c r="H6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1634,11 +1631,11 @@
       <c r="F7" t="s">
         <v>34</v>
       </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1657,11 +1654,11 @@
       <c r="F8" t="s">
         <v>34</v>
       </c>
-      <c r="H8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1680,11 +1677,11 @@
       <c r="F9" t="s">
         <v>34</v>
       </c>
-      <c r="H9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1703,11 +1700,11 @@
       <c r="F10" t="s">
         <v>34</v>
       </c>
-      <c r="H10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1726,11 +1723,11 @@
       <c r="F11" t="s">
         <v>34</v>
       </c>
-      <c r="H11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1749,11 +1746,11 @@
       <c r="F12" t="s">
         <v>34</v>
       </c>
-      <c r="H12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1772,11 +1769,11 @@
       <c r="F13" t="s">
         <v>34</v>
       </c>
-      <c r="H13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -1795,11 +1792,11 @@
       <c r="F14" t="s">
         <v>62</v>
       </c>
-      <c r="H14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1818,11 +1815,11 @@
       <c r="F15" t="s">
         <v>62</v>
       </c>
-      <c r="H15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1841,11 +1838,11 @@
       <c r="F16" t="s">
         <v>34</v>
       </c>
-      <c r="H16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1867,11 +1864,11 @@
       <c r="G17" t="s">
         <v>73</v>
       </c>
-      <c r="H17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1890,11 +1887,11 @@
       <c r="F18" t="s">
         <v>34</v>
       </c>
-      <c r="H18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1913,11 +1910,11 @@
       <c r="F19" t="s">
         <v>34</v>
       </c>
-      <c r="H19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1936,11 +1933,11 @@
       <c r="F20" t="s">
         <v>34</v>
       </c>
-      <c r="H20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1959,11 +1956,11 @@
       <c r="F21" t="s">
         <v>34</v>
       </c>
-      <c r="H21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1985,11 +1982,11 @@
       <c r="G22" t="s">
         <v>89</v>
       </c>
-      <c r="H22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2008,11 +2005,11 @@
       <c r="F23" t="s">
         <v>34</v>
       </c>
-      <c r="H23" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2034,11 +2031,11 @@
       <c r="G24" t="s">
         <v>89</v>
       </c>
-      <c r="H24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2060,11 +2057,11 @@
       <c r="G25" t="s">
         <v>99</v>
       </c>
-      <c r="H25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -2086,11 +2083,11 @@
       <c r="G26" t="s">
         <v>99</v>
       </c>
-      <c r="H26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -2112,11 +2109,11 @@
       <c r="G27" t="s">
         <v>99</v>
       </c>
-      <c r="H27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -2138,11 +2135,11 @@
       <c r="G28" t="s">
         <v>89</v>
       </c>
-      <c r="H28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -2164,11 +2161,11 @@
       <c r="G29" t="s">
         <v>112</v>
       </c>
-      <c r="H29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -2190,11 +2187,11 @@
       <c r="G30" t="s">
         <v>112</v>
       </c>
-      <c r="H30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>23</v>
       </c>
@@ -2216,11 +2213,11 @@
       <c r="G31" t="s">
         <v>112</v>
       </c>
-      <c r="H31" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>23</v>
       </c>
@@ -2242,11 +2239,11 @@
       <c r="G32" t="s">
         <v>112</v>
       </c>
-      <c r="H32" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>23</v>
       </c>
@@ -2268,11 +2265,11 @@
       <c r="G33" t="s">
         <v>125</v>
       </c>
-      <c r="H33" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>23</v>
       </c>
@@ -2294,11 +2291,11 @@
       <c r="G34" t="s">
         <v>129</v>
       </c>
-      <c r="H34" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>23</v>
       </c>
@@ -2320,11 +2317,11 @@
       <c r="G35" t="s">
         <v>133</v>
       </c>
-      <c r="H35" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I35" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>23</v>
       </c>
@@ -2346,11 +2343,11 @@
       <c r="G36" t="s">
         <v>137</v>
       </c>
-      <c r="H36" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>23</v>
       </c>
@@ -2372,11 +2369,11 @@
       <c r="G37" t="s">
         <v>133</v>
       </c>
-      <c r="H37" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>23</v>
       </c>
@@ -2398,11 +2395,11 @@
       <c r="G38" t="s">
         <v>137</v>
       </c>
-      <c r="H38" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I38" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>23</v>
       </c>
@@ -2424,11 +2421,11 @@
       <c r="G39" t="s">
         <v>73</v>
       </c>
-      <c r="H39" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I39" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -2450,11 +2447,11 @@
       <c r="G40" t="s">
         <v>73</v>
       </c>
-      <c r="H40" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>23</v>
       </c>
@@ -2476,11 +2473,11 @@
       <c r="G41" t="s">
         <v>73</v>
       </c>
-      <c r="H41" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -2499,11 +2496,11 @@
       <c r="F42" t="s">
         <v>34</v>
       </c>
-      <c r="H42" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>23</v>
       </c>
@@ -2522,11 +2519,11 @@
       <c r="F43" t="s">
         <v>34</v>
       </c>
-      <c r="H43" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I43" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>23</v>
       </c>
@@ -2545,11 +2542,11 @@
       <c r="F44" t="s">
         <v>34</v>
       </c>
-      <c r="H44" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I44" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>23</v>
       </c>
@@ -2568,11 +2565,11 @@
       <c r="F45" t="s">
         <v>34</v>
       </c>
-      <c r="H45" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>23</v>
       </c>
@@ -2591,11 +2588,11 @@
       <c r="F46" t="s">
         <v>34</v>
       </c>
-      <c r="H46" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I46" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>23</v>
       </c>
@@ -2617,11 +2614,11 @@
       <c r="G47" t="s">
         <v>73</v>
       </c>
-      <c r="H47" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -2640,11 +2637,11 @@
       <c r="F48" t="s">
         <v>34</v>
       </c>
-      <c r="H48" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I48" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>23</v>
       </c>
@@ -2663,11 +2660,11 @@
       <c r="F49" t="s">
         <v>34</v>
       </c>
-      <c r="H49" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I49" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>23</v>
       </c>
@@ -2686,11 +2683,11 @@
       <c r="F50" t="s">
         <v>34</v>
       </c>
-      <c r="H50" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>23</v>
       </c>
@@ -2709,11 +2706,11 @@
       <c r="F51" t="s">
         <v>34</v>
       </c>
-      <c r="H51" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -2732,11 +2729,11 @@
       <c r="F52" t="s">
         <v>34</v>
       </c>
-      <c r="H52" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I52" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>23</v>
       </c>
@@ -2755,11 +2752,11 @@
       <c r="F53" t="s">
         <v>34</v>
       </c>
-      <c r="H53" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I53" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>23</v>
       </c>
@@ -2778,11 +2775,11 @@
       <c r="F54" t="s">
         <v>34</v>
       </c>
-      <c r="H54" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I54" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>23</v>
       </c>
@@ -2804,11 +2801,11 @@
       <c r="G55" t="s">
         <v>194</v>
       </c>
-      <c r="H55" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>23</v>
       </c>
@@ -2827,11 +2824,11 @@
       <c r="F56" t="s">
         <v>34</v>
       </c>
-      <c r="H56" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I56" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>23</v>
       </c>
@@ -2850,11 +2847,11 @@
       <c r="F57" t="s">
         <v>34</v>
       </c>
-      <c r="H57" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I57" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>23</v>
       </c>
@@ -2873,11 +2870,11 @@
       <c r="F58" t="s">
         <v>34</v>
       </c>
-      <c r="H58" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>23</v>
       </c>
@@ -2896,11 +2893,11 @@
       <c r="F59" t="s">
         <v>34</v>
       </c>
-      <c r="H59" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I59" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>23</v>
       </c>
@@ -2919,11 +2916,11 @@
       <c r="F60" t="s">
         <v>34</v>
       </c>
-      <c r="H60" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I60" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>23</v>
       </c>
@@ -2942,11 +2939,11 @@
       <c r="F61" t="s">
         <v>34</v>
       </c>
-      <c r="H61" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I61" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>23</v>
       </c>
@@ -2965,11 +2962,11 @@
       <c r="F62" t="s">
         <v>34</v>
       </c>
-      <c r="H62" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I62" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>23</v>
       </c>
@@ -2988,11 +2985,11 @@
       <c r="F63" t="s">
         <v>34</v>
       </c>
-      <c r="H63" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I63" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>23</v>
       </c>
@@ -3014,11 +3011,11 @@
       <c r="G64" t="s">
         <v>194</v>
       </c>
-      <c r="H64" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I64" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>23</v>
       </c>
@@ -3037,11 +3034,11 @@
       <c r="F65" t="s">
         <v>62</v>
       </c>
-      <c r="H65" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I65" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>23</v>
       </c>
@@ -3063,11 +3060,11 @@
       <c r="G66" t="s">
         <v>194</v>
       </c>
-      <c r="H66" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I66" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>23</v>
       </c>
@@ -3086,11 +3083,11 @@
       <c r="F67" t="s">
         <v>62</v>
       </c>
-      <c r="H67" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I67" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>23</v>
       </c>
@@ -3109,11 +3106,11 @@
       <c r="F68" t="s">
         <v>34</v>
       </c>
-      <c r="H68" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I68" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>23</v>
       </c>
@@ -3132,11 +3129,11 @@
       <c r="F69" t="s">
         <v>62</v>
       </c>
-      <c r="H69" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I69" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>23</v>
       </c>
@@ -3155,11 +3152,11 @@
       <c r="F70" t="s">
         <v>62</v>
       </c>
-      <c r="H70" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I70" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>23</v>
       </c>
@@ -3178,11 +3175,11 @@
       <c r="F71" t="s">
         <v>62</v>
       </c>
-      <c r="H71" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I71" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>23</v>
       </c>
@@ -3201,11 +3198,11 @@
       <c r="F72" t="s">
         <v>62</v>
       </c>
-      <c r="H72" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I72" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>23</v>
       </c>
@@ -3224,11 +3221,11 @@
       <c r="F73" t="s">
         <v>62</v>
       </c>
-      <c r="H73" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I73" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>23</v>
       </c>
@@ -3250,11 +3247,11 @@
       <c r="G74" t="s">
         <v>194</v>
       </c>
-      <c r="H74" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I74" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>23</v>
       </c>
@@ -3273,11 +3270,11 @@
       <c r="F75" t="s">
         <v>34</v>
       </c>
-      <c r="H75" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I75" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>23</v>
       </c>
@@ -3296,11 +3293,11 @@
       <c r="F76" t="s">
         <v>34</v>
       </c>
-      <c r="H76" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I76" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>23</v>
       </c>
@@ -3319,11 +3316,11 @@
       <c r="F77" t="s">
         <v>34</v>
       </c>
-      <c r="H77" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I77" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>23</v>
       </c>
@@ -3342,11 +3339,11 @@
       <c r="F78" t="s">
         <v>34</v>
       </c>
-      <c r="H78" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I78" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>23</v>
       </c>
@@ -3365,11 +3362,11 @@
       <c r="F79" t="s">
         <v>34</v>
       </c>
-      <c r="H79" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I79" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>23</v>
       </c>
@@ -3388,11 +3385,11 @@
       <c r="F80" t="s">
         <v>34</v>
       </c>
-      <c r="H80" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I80" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>23</v>
       </c>
@@ -3411,11 +3408,11 @@
       <c r="F81" t="s">
         <v>34</v>
       </c>
-      <c r="H81" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I81" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -3434,11 +3431,11 @@
       <c r="F82" t="s">
         <v>34</v>
       </c>
-      <c r="H82" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I82" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>23</v>
       </c>
@@ -3457,11 +3454,11 @@
       <c r="F83" t="s">
         <v>34</v>
       </c>
-      <c r="H83" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I83" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>23</v>
       </c>
@@ -3480,11 +3477,11 @@
       <c r="F84" t="s">
         <v>34</v>
       </c>
-      <c r="H84" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I84" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>23</v>
       </c>
@@ -3503,11 +3500,11 @@
       <c r="F85" t="s">
         <v>34</v>
       </c>
-      <c r="H85" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I85" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>23</v>
       </c>
@@ -3526,11 +3523,11 @@
       <c r="F86" t="s">
         <v>34</v>
       </c>
-      <c r="H86" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I86" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>23</v>
       </c>
@@ -3549,7 +3546,7 @@
       <c r="F87" t="s">
         <v>34</v>
       </c>
-      <c r="H87" t="s">
+      <c r="I87" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3561,21 +3558,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3607,7 +3604,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -3627,7 +3624,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -3647,7 +3644,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -3667,7 +3664,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>

--- a/docs/resources/Dictionary_testNetwork.xlsx
+++ b/docs/resources/Dictionary_testNetwork.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89ACE056-AAD2-4CAE-8285-59AB42B12C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8871B628-AFBE-4AB3-976E-835FBCB947AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -954,7 +954,7 @@
     <t>variable</t>
   </si>
   <si>
-    <t>http://snomed.info/id/903121</t>
+    <t>http://snomed.info/id/27113001</t>
   </si>
 </sst>
 </file>

--- a/docs/resources/Dictionary_testNetwork.xlsx
+++ b/docs/resources/Dictionary_testNetwork.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301311DE-E90B-4645-9FF2-BEA03B89E409}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCC6458-84FE-4E60-B489-DE8BA1632065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -954,17 +954,25 @@
     <t>useExternalDefinition.table</t>
   </si>
   <si>
-    <t>http://snomed.info/id/903121</t>
+    <t>http://snomed.info/id/27113001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -987,13 +995,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1505,7 +1516,7 @@
       <c r="G2" t="s">
         <v>298</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>310</v>
       </c>
       <c r="I2" t="s">
@@ -3564,6 +3575,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{57A76777-157A-4CC4-8C4D-61F7A119A5AD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/docs/resources/Dictionary_testNetwork.xlsx
+++ b/docs/resources/Dictionary_testNetwork.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brend\Molgenis\repos\molgenis-emx2\docs\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5E0291D-0A1C-401F-8DE7-2A64BE49F1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8871B628-AFBE-4AB3-976E-835FBCB947AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="19185" windowHeight="11985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datasets" sheetId="6" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="311">
   <si>
     <t>label</t>
   </si>
@@ -952,6 +952,9 @@
   </si>
   <si>
     <t>variable</t>
+  </si>
+  <si>
+    <t>http://snomed.info/id/27113001</t>
   </si>
 </sst>
 </file>
@@ -1323,22 +1326,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.9296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.06640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1363,14 +1366,14 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1383,7 +1386,7 @@
       <c r="G2" t="s">
         <v>26</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1394,30 +1397,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:S87"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:T87"/>
+  <sheetFormatPr defaultColWidth="8.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.9296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.73046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="216.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.59765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.1328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.06640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.19921875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="24.1328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5546875" customWidth="1"/>
+    <col min="5" max="5" width="39.21875" customWidth="1"/>
+    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1440,43 +1431,46 @@
         <v>16</v>
       </c>
       <c r="H1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>17</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>18</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>19</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>6</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>21</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>28</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>29</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>30</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1499,19 +1493,22 @@
         <v>301</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" t="s">
+        <v>310</v>
+      </c>
+      <c r="I2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K2" t="s">
         <v>302</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>270</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1533,20 +1530,20 @@
       <c r="G3" t="s">
         <v>305</v>
       </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="I3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
         <v>302</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>270</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1565,11 +1562,11 @@
       <c r="F4" t="s">
         <v>34</v>
       </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1588,11 +1585,11 @@
       <c r="F5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1611,11 +1608,11 @@
       <c r="F6" t="s">
         <v>34</v>
       </c>
-      <c r="H6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -1634,11 +1631,11 @@
       <c r="F7" t="s">
         <v>34</v>
       </c>
-      <c r="H7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1657,11 +1654,11 @@
       <c r="F8" t="s">
         <v>34</v>
       </c>
-      <c r="H8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1680,11 +1677,11 @@
       <c r="F9" t="s">
         <v>34</v>
       </c>
-      <c r="H9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>23</v>
       </c>
@@ -1703,11 +1700,11 @@
       <c r="F10" t="s">
         <v>34</v>
       </c>
-      <c r="H10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -1726,11 +1723,11 @@
       <c r="F11" t="s">
         <v>34</v>
       </c>
-      <c r="H11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1749,11 +1746,11 @@
       <c r="F12" t="s">
         <v>34</v>
       </c>
-      <c r="H12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1772,11 +1769,11 @@
       <c r="F13" t="s">
         <v>34</v>
       </c>
-      <c r="H13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -1795,11 +1792,11 @@
       <c r="F14" t="s">
         <v>62</v>
       </c>
-      <c r="H14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1818,11 +1815,11 @@
       <c r="F15" t="s">
         <v>62</v>
       </c>
-      <c r="H15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="I15" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1841,11 +1838,11 @@
       <c r="F16" t="s">
         <v>34</v>
       </c>
-      <c r="H16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1867,11 +1864,11 @@
       <c r="G17" t="s">
         <v>73</v>
       </c>
-      <c r="H17" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1890,11 +1887,11 @@
       <c r="F18" t="s">
         <v>34</v>
       </c>
-      <c r="H18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1913,11 +1910,11 @@
       <c r="F19" t="s">
         <v>34</v>
       </c>
-      <c r="H19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1936,11 +1933,11 @@
       <c r="F20" t="s">
         <v>34</v>
       </c>
-      <c r="H20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1959,11 +1956,11 @@
       <c r="F21" t="s">
         <v>34</v>
       </c>
-      <c r="H21" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1985,11 +1982,11 @@
       <c r="G22" t="s">
         <v>89</v>
       </c>
-      <c r="H22" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2008,11 +2005,11 @@
       <c r="F23" t="s">
         <v>34</v>
       </c>
-      <c r="H23" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I23" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -2034,11 +2031,11 @@
       <c r="G24" t="s">
         <v>89</v>
       </c>
-      <c r="H24" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I24" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -2060,11 +2057,11 @@
       <c r="G25" t="s">
         <v>99</v>
       </c>
-      <c r="H25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -2086,11 +2083,11 @@
       <c r="G26" t="s">
         <v>99</v>
       </c>
-      <c r="H26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -2112,11 +2109,11 @@
       <c r="G27" t="s">
         <v>99</v>
       </c>
-      <c r="H27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -2138,11 +2135,11 @@
       <c r="G28" t="s">
         <v>89</v>
       </c>
-      <c r="H28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>23</v>
       </c>
@@ -2164,11 +2161,11 @@
       <c r="G29" t="s">
         <v>112</v>
       </c>
-      <c r="H29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>23</v>
       </c>
@@ -2190,11 +2187,11 @@
       <c r="G30" t="s">
         <v>112</v>
       </c>
-      <c r="H30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>23</v>
       </c>
@@ -2216,11 +2213,11 @@
       <c r="G31" t="s">
         <v>112</v>
       </c>
-      <c r="H31" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>23</v>
       </c>
@@ -2242,11 +2239,11 @@
       <c r="G32" t="s">
         <v>112</v>
       </c>
-      <c r="H32" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>23</v>
       </c>
@@ -2268,11 +2265,11 @@
       <c r="G33" t="s">
         <v>125</v>
       </c>
-      <c r="H33" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I33" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>23</v>
       </c>
@@ -2294,11 +2291,11 @@
       <c r="G34" t="s">
         <v>129</v>
       </c>
-      <c r="H34" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>23</v>
       </c>
@@ -2320,11 +2317,11 @@
       <c r="G35" t="s">
         <v>133</v>
       </c>
-      <c r="H35" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I35" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>23</v>
       </c>
@@ -2346,11 +2343,11 @@
       <c r="G36" t="s">
         <v>137</v>
       </c>
-      <c r="H36" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I36" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>23</v>
       </c>
@@ -2372,11 +2369,11 @@
       <c r="G37" t="s">
         <v>133</v>
       </c>
-      <c r="H37" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I37" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>23</v>
       </c>
@@ -2398,11 +2395,11 @@
       <c r="G38" t="s">
         <v>137</v>
       </c>
-      <c r="H38" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I38" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>23</v>
       </c>
@@ -2424,11 +2421,11 @@
       <c r="G39" t="s">
         <v>73</v>
       </c>
-      <c r="H39" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I39" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>23</v>
       </c>
@@ -2450,11 +2447,11 @@
       <c r="G40" t="s">
         <v>73</v>
       </c>
-      <c r="H40" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I40" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>23</v>
       </c>
@@ -2476,11 +2473,11 @@
       <c r="G41" t="s">
         <v>73</v>
       </c>
-      <c r="H41" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>23</v>
       </c>
@@ -2499,11 +2496,11 @@
       <c r="F42" t="s">
         <v>34</v>
       </c>
-      <c r="H42" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>23</v>
       </c>
@@ -2522,11 +2519,11 @@
       <c r="F43" t="s">
         <v>34</v>
       </c>
-      <c r="H43" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I43" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>23</v>
       </c>
@@ -2545,11 +2542,11 @@
       <c r="F44" t="s">
         <v>34</v>
       </c>
-      <c r="H44" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I44" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>23</v>
       </c>
@@ -2568,11 +2565,11 @@
       <c r="F45" t="s">
         <v>34</v>
       </c>
-      <c r="H45" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>23</v>
       </c>
@@ -2591,11 +2588,11 @@
       <c r="F46" t="s">
         <v>34</v>
       </c>
-      <c r="H46" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I46" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>23</v>
       </c>
@@ -2617,11 +2614,11 @@
       <c r="G47" t="s">
         <v>73</v>
       </c>
-      <c r="H47" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -2640,11 +2637,11 @@
       <c r="F48" t="s">
         <v>34</v>
       </c>
-      <c r="H48" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I48" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>23</v>
       </c>
@@ -2663,11 +2660,11 @@
       <c r="F49" t="s">
         <v>34</v>
       </c>
-      <c r="H49" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I49" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>23</v>
       </c>
@@ -2686,11 +2683,11 @@
       <c r="F50" t="s">
         <v>34</v>
       </c>
-      <c r="H50" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>23</v>
       </c>
@@ -2709,11 +2706,11 @@
       <c r="F51" t="s">
         <v>34</v>
       </c>
-      <c r="H51" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I51" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>23</v>
       </c>
@@ -2732,11 +2729,11 @@
       <c r="F52" t="s">
         <v>34</v>
       </c>
-      <c r="H52" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I52" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>23</v>
       </c>
@@ -2755,11 +2752,11 @@
       <c r="F53" t="s">
         <v>34</v>
       </c>
-      <c r="H53" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I53" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>23</v>
       </c>
@@ -2778,11 +2775,11 @@
       <c r="F54" t="s">
         <v>34</v>
       </c>
-      <c r="H54" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I54" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>23</v>
       </c>
@@ -2804,11 +2801,11 @@
       <c r="G55" t="s">
         <v>194</v>
       </c>
-      <c r="H55" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I55" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>23</v>
       </c>
@@ -2827,11 +2824,11 @@
       <c r="F56" t="s">
         <v>34</v>
       </c>
-      <c r="H56" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I56" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>23</v>
       </c>
@@ -2850,11 +2847,11 @@
       <c r="F57" t="s">
         <v>34</v>
       </c>
-      <c r="H57" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I57" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>23</v>
       </c>
@@ -2873,11 +2870,11 @@
       <c r="F58" t="s">
         <v>34</v>
       </c>
-      <c r="H58" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>23</v>
       </c>
@@ -2896,11 +2893,11 @@
       <c r="F59" t="s">
         <v>34</v>
       </c>
-      <c r="H59" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I59" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>23</v>
       </c>
@@ -2919,11 +2916,11 @@
       <c r="F60" t="s">
         <v>34</v>
       </c>
-      <c r="H60" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I60" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>23</v>
       </c>
@@ -2942,11 +2939,11 @@
       <c r="F61" t="s">
         <v>34</v>
       </c>
-      <c r="H61" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I61" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>23</v>
       </c>
@@ -2965,11 +2962,11 @@
       <c r="F62" t="s">
         <v>34</v>
       </c>
-      <c r="H62" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I62" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>23</v>
       </c>
@@ -2988,11 +2985,11 @@
       <c r="F63" t="s">
         <v>34</v>
       </c>
-      <c r="H63" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I63" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>23</v>
       </c>
@@ -3014,11 +3011,11 @@
       <c r="G64" t="s">
         <v>194</v>
       </c>
-      <c r="H64" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I64" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>23</v>
       </c>
@@ -3037,11 +3034,11 @@
       <c r="F65" t="s">
         <v>62</v>
       </c>
-      <c r="H65" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I65" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>23</v>
       </c>
@@ -3063,11 +3060,11 @@
       <c r="G66" t="s">
         <v>194</v>
       </c>
-      <c r="H66" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I66" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>23</v>
       </c>
@@ -3086,11 +3083,11 @@
       <c r="F67" t="s">
         <v>62</v>
       </c>
-      <c r="H67" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I67" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>23</v>
       </c>
@@ -3109,11 +3106,11 @@
       <c r="F68" t="s">
         <v>34</v>
       </c>
-      <c r="H68" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I68" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>23</v>
       </c>
@@ -3132,11 +3129,11 @@
       <c r="F69" t="s">
         <v>62</v>
       </c>
-      <c r="H69" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I69" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>23</v>
       </c>
@@ -3155,11 +3152,11 @@
       <c r="F70" t="s">
         <v>62</v>
       </c>
-      <c r="H70" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I70" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>23</v>
       </c>
@@ -3178,11 +3175,11 @@
       <c r="F71" t="s">
         <v>62</v>
       </c>
-      <c r="H71" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I71" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>23</v>
       </c>
@@ -3201,11 +3198,11 @@
       <c r="F72" t="s">
         <v>62</v>
       </c>
-      <c r="H72" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I72" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>23</v>
       </c>
@@ -3224,11 +3221,11 @@
       <c r="F73" t="s">
         <v>62</v>
       </c>
-      <c r="H73" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I73" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>23</v>
       </c>
@@ -3250,11 +3247,11 @@
       <c r="G74" t="s">
         <v>194</v>
       </c>
-      <c r="H74" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I74" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>23</v>
       </c>
@@ -3273,11 +3270,11 @@
       <c r="F75" t="s">
         <v>34</v>
       </c>
-      <c r="H75" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I75" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>23</v>
       </c>
@@ -3296,11 +3293,11 @@
       <c r="F76" t="s">
         <v>34</v>
       </c>
-      <c r="H76" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I76" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>23</v>
       </c>
@@ -3319,11 +3316,11 @@
       <c r="F77" t="s">
         <v>34</v>
       </c>
-      <c r="H77" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I77" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>23</v>
       </c>
@@ -3342,11 +3339,11 @@
       <c r="F78" t="s">
         <v>34</v>
       </c>
-      <c r="H78" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I78" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>23</v>
       </c>
@@ -3365,11 +3362,11 @@
       <c r="F79" t="s">
         <v>34</v>
       </c>
-      <c r="H79" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I79" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>23</v>
       </c>
@@ -3388,11 +3385,11 @@
       <c r="F80" t="s">
         <v>34</v>
       </c>
-      <c r="H80" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I80" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>23</v>
       </c>
@@ -3411,11 +3408,11 @@
       <c r="F81" t="s">
         <v>34</v>
       </c>
-      <c r="H81" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I81" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>23</v>
       </c>
@@ -3434,11 +3431,11 @@
       <c r="F82" t="s">
         <v>34</v>
       </c>
-      <c r="H82" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I82" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>23</v>
       </c>
@@ -3457,11 +3454,11 @@
       <c r="F83" t="s">
         <v>34</v>
       </c>
-      <c r="H83" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I83" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>23</v>
       </c>
@@ -3480,11 +3477,11 @@
       <c r="F84" t="s">
         <v>34</v>
       </c>
-      <c r="H84" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I84" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>23</v>
       </c>
@@ -3503,11 +3500,11 @@
       <c r="F85" t="s">
         <v>34</v>
       </c>
-      <c r="H85" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I85" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>23</v>
       </c>
@@ -3526,11 +3523,11 @@
       <c r="F86" t="s">
         <v>34</v>
       </c>
-      <c r="H86" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="I86" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>23</v>
       </c>
@@ -3549,7 +3546,7 @@
       <c r="F87" t="s">
         <v>34</v>
       </c>
-      <c r="H87" t="s">
+      <c r="I87" t="s">
         <v>27</v>
       </c>
     </row>
@@ -3561,21 +3558,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3607,7 +3604,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -3627,7 +3624,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -3647,7 +3644,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -3667,7 +3664,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>

--- a/docs/resources/Dictionary_testNetwork.xlsx
+++ b/docs/resources/Dictionary_testNetwork.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HijmansBS\Molgenis\repos\molgenis-emx2\docs\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8871B628-AFBE-4AB3-976E-835FBCB947AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FCC6458-84FE-4E60-B489-DE8BA1632065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Datasets" sheetId="6" r:id="rId1"/>
+    <sheet name="Tables" sheetId="6" r:id="rId1"/>
     <sheet name="Variables" sheetId="9" r:id="rId2"/>
     <sheet name="Variable values" sheetId="14" r:id="rId3"/>
   </sheets>
@@ -36,9 +36,6 @@
     <t>name</t>
   </si>
   <si>
-    <t>dataset type</t>
-  </si>
-  <si>
     <t>unit of observation</t>
   </si>
   <si>
@@ -66,9 +63,6 @@
     <t>ontology term URI</t>
   </si>
   <si>
-    <t>dataset</t>
-  </si>
-  <si>
     <t>format</t>
   </si>
   <si>
@@ -111,9 +105,6 @@
     <t>useExternalDefinition.resource</t>
   </si>
   <si>
-    <t>useExternalDefinition.dataset</t>
-  </si>
-  <si>
     <t>useExternalDefinition.name</t>
   </si>
   <si>
@@ -952,6 +943,15 @@
   </si>
   <si>
     <t>variable</t>
+  </si>
+  <si>
+    <t>table type</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
+    <t>useExternalDefinition.table</t>
   </si>
   <si>
     <t>http://snomed.info/id/27113001</t>
@@ -961,10 +961,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -987,13 +995,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1326,7 +1337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
@@ -1337,11 +1348,11 @@
     <col min="6" max="6" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1352,42 +1363,42 @@
         <v>0</v>
       </c>
       <c r="D1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
       </c>
       <c r="G1" t="s">
         <v>1</v>
       </c>
       <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
         <v>7</v>
       </c>
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" t="s">
+      <c r="G2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" t="s">
-        <v>27</v>
+      <c r="I2" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1398,14 +1409,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:T87"/>
-  <sheetFormatPr defaultColWidth="8.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.5546875" customWidth="1"/>
-    <col min="5" max="5" width="39.21875" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.5546875" customWidth="1"/>
+    <col min="5" max="5" width="60.21875" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
@@ -1413,7 +1437,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>308</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
@@ -1425,81 +1449,81 @@
         <v>1</v>
       </c>
       <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
         <v>15</v>
       </c>
-      <c r="G1" t="s">
+      <c r="L1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>17</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>18</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
+        <v>26</v>
+      </c>
+      <c r="R1" t="s">
+        <v>309</v>
+      </c>
+      <c r="S1" t="s">
+        <v>27</v>
+      </c>
+      <c r="T1" t="s">
         <v>20</v>
-      </c>
-      <c r="O1" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>28</v>
-      </c>
-      <c r="R1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S1" t="s">
-        <v>30</v>
-      </c>
-      <c r="T1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" t="s">
+        <v>298</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K2" t="s">
         <v>299</v>
-      </c>
-      <c r="F2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G2" t="s">
-        <v>301</v>
-      </c>
-      <c r="H2" t="s">
-        <v>310</v>
-      </c>
-      <c r="I2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" t="s">
-        <v>302</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1510,31 +1534,31 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1545,2012 +1569,2015 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" t="s">
         <v>59</v>
       </c>
-      <c r="D14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
       <c r="I14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" t="s">
         <v>69</v>
       </c>
-      <c r="D17" t="s">
+      <c r="G17" t="s">
         <v>70</v>
       </c>
-      <c r="E17" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17" t="s">
-        <v>73</v>
-      </c>
       <c r="I17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I18" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E20" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I20" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F21" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" t="s">
         <v>86</v>
       </c>
-      <c r="D22" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" t="s">
-        <v>88</v>
-      </c>
-      <c r="F22" t="s">
-        <v>72</v>
-      </c>
-      <c r="G22" t="s">
-        <v>89</v>
-      </c>
       <c r="I22" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F23" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G24" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I24" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" t="s">
         <v>96</v>
       </c>
-      <c r="D25" t="s">
-        <v>97</v>
-      </c>
-      <c r="E25" t="s">
-        <v>98</v>
-      </c>
-      <c r="F25" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" t="s">
-        <v>99</v>
-      </c>
       <c r="I25" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F26" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G26" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E27" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F27" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G27" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F28" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G28" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" t="s">
         <v>109</v>
       </c>
-      <c r="D29" t="s">
-        <v>110</v>
-      </c>
-      <c r="E29" t="s">
-        <v>111</v>
-      </c>
-      <c r="F29" t="s">
-        <v>72</v>
-      </c>
-      <c r="G29" t="s">
-        <v>112</v>
-      </c>
       <c r="I29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D30" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E30" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F30" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G30" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D31" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E31" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F31" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G31" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E32" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F32" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G32" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="I32" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C33" t="s">
+        <v>119</v>
+      </c>
+      <c r="D33" t="s">
+        <v>120</v>
+      </c>
+      <c r="E33" t="s">
+        <v>121</v>
+      </c>
+      <c r="F33" t="s">
+        <v>69</v>
+      </c>
+      <c r="G33" t="s">
         <v>122</v>
       </c>
-      <c r="D33" t="s">
-        <v>123</v>
-      </c>
-      <c r="E33" t="s">
-        <v>124</v>
-      </c>
-      <c r="F33" t="s">
-        <v>72</v>
-      </c>
-      <c r="G33" t="s">
-        <v>125</v>
-      </c>
       <c r="I33" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C34" t="s">
+        <v>123</v>
+      </c>
+      <c r="D34" t="s">
+        <v>124</v>
+      </c>
+      <c r="E34" t="s">
+        <v>125</v>
+      </c>
+      <c r="F34" t="s">
+        <v>69</v>
+      </c>
+      <c r="G34" t="s">
         <v>126</v>
       </c>
-      <c r="D34" t="s">
-        <v>127</v>
-      </c>
-      <c r="E34" t="s">
-        <v>128</v>
-      </c>
-      <c r="F34" t="s">
-        <v>72</v>
-      </c>
-      <c r="G34" t="s">
-        <v>129</v>
-      </c>
       <c r="I34" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C35" t="s">
+        <v>127</v>
+      </c>
+      <c r="D35" t="s">
+        <v>128</v>
+      </c>
+      <c r="E35" t="s">
+        <v>129</v>
+      </c>
+      <c r="F35" t="s">
+        <v>69</v>
+      </c>
+      <c r="G35" t="s">
         <v>130</v>
       </c>
-      <c r="D35" t="s">
-        <v>131</v>
-      </c>
-      <c r="E35" t="s">
-        <v>132</v>
-      </c>
-      <c r="F35" t="s">
-        <v>72</v>
-      </c>
-      <c r="G35" t="s">
-        <v>133</v>
-      </c>
       <c r="I35" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C36" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" t="s">
+        <v>132</v>
+      </c>
+      <c r="E36" t="s">
+        <v>133</v>
+      </c>
+      <c r="F36" t="s">
+        <v>69</v>
+      </c>
+      <c r="G36" t="s">
         <v>134</v>
       </c>
-      <c r="D36" t="s">
-        <v>135</v>
-      </c>
-      <c r="E36" t="s">
-        <v>136</v>
-      </c>
-      <c r="F36" t="s">
-        <v>72</v>
-      </c>
-      <c r="G36" t="s">
-        <v>137</v>
-      </c>
       <c r="I36" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D37" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E37" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F37" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G37" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I37" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D38" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E38" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G38" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I38" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D39" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E39" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F39" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G39" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I39" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D40" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E40" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F40" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G40" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I40" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D41" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E41" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F41" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G41" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I41" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D42" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E42" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F42" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I42" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D43" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E43" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F43" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I43" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C44" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D44" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E44" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F44" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I44" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C45" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D45" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E45" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F45" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I45" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C46" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D46" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E46" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F46" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I46" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C47" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D47" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E47" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F47" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G47" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I47" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C48" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D48" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E48" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F48" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I48" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C49" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D49" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E49" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F49" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I49" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B50" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C50" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D50" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E50" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F50" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I50" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B51" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C51" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D51" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E51" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F51" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I51" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B52" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C52" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D52" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E52" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F52" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I52" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B53" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C53" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="D53" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E53" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F53" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I53" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C54" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D54" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E54" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F54" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I54" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C55" t="s">
+        <v>188</v>
+      </c>
+      <c r="D55" t="s">
+        <v>189</v>
+      </c>
+      <c r="E55" t="s">
+        <v>190</v>
+      </c>
+      <c r="F55" t="s">
+        <v>69</v>
+      </c>
+      <c r="G55" t="s">
         <v>191</v>
       </c>
-      <c r="D55" t="s">
-        <v>192</v>
-      </c>
-      <c r="E55" t="s">
-        <v>193</v>
-      </c>
-      <c r="F55" t="s">
-        <v>72</v>
-      </c>
-      <c r="G55" t="s">
-        <v>194</v>
-      </c>
       <c r="I55" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C56" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D56" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E56" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F56" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I56" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C57" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D57" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E57" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F57" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I57" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C58" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D58" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E58" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F58" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I58" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C59" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D59" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E59" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F59" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I59" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C60" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D60" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E60" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F60" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I60" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B61" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C61" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D61" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E61" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F61" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I61" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C62" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D62" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E62" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F62" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I62" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B63" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C63" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D63" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E63" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F63" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I63" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C64" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D64" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E64" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F64" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G64" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I64" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C65" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D65" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E65" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F65" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I65" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C66" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D66" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E66" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F66" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G66" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I66" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B67" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C67" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D67" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E67" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F67" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I67" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C68" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D68" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E68" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F68" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I68" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B69" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C69" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D69" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E69" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F69" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I69" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B70" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C70" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D70" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E70" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F70" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I70" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B71" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C71" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D71" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E71" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F71" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I71" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C72" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D72" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E72" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F72" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I72" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C73" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D73" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E73" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F73" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I73" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B74" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C74" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D74" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E74" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F74" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G74" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I74" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B75" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C75" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D75" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E75" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F75" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I75" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C76" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D76" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E76" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F76" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I76" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C77" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D77" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E77" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F77" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I77" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B78" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C78" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D78" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E78" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F78" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I78" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B79" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C79" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D79" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E79" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F79" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I79" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C80" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D80" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E80" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F80" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I80" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C81" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D81" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E81" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F81" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I81" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B82" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C82" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D82" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E82" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F82" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I82" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C83" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D83" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E83" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F83" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I83" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B84" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C84" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D84" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E84" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F84" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I84" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B85" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C85" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D85" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E85" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F85" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I85" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B86" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C86" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D86" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E86" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F86" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I86" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B87" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C87" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D87" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E87" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F87" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="I87" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{57A76777-157A-4CC4-8C4D-61F7A119A5AD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3577,111 +3604,111 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>308</v>
       </c>
       <c r="C1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
       </c>
       <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>12</v>
       </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
       <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
